--- a/data/MPI.xlsx
+++ b/data/MPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\damaso.hernandez\Desktop\Videos\Backup. Damaso hernandez\0.CARPERTA CORDINACION\0.CORDINACION ANALITICA\18. PERSONAL\ANALISIS_AGUAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2258BA4A-B4B3-4C4F-8FBD-6C0B8829FFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF452D98-5B93-4542-BF41-10EF8CE763D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EB66CE8F-5A8B-46C2-A2A0-B15EB23AB4EF}"/>
   </bookViews>
@@ -196,7 +196,7 @@
     <t>Población_total</t>
   </si>
   <si>
-    <t>Población_Cp</t>
+    <t>Población_CM</t>
   </si>
   <si>
     <t>Población_CP</t>

--- a/data/MPI.xlsx
+++ b/data/MPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\damaso.hernandez\Desktop\Videos\Backup. Damaso hernandez\0.CARPERTA CORDINACION\0.CORDINACION ANALITICA\18. PERSONAL\ANALISIS_AGUAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF452D98-5B93-4542-BF41-10EF8CE763D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF6EE38-BC11-425E-8085-82D176BFAB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EB66CE8F-5A8B-46C2-A2A0-B15EB23AB4EF}"/>
   </bookViews>
